--- a/results/naturverbundenheit/base_data/nature-dataset_sample_size.xlsx
+++ b/results/naturverbundenheit/base_data/nature-dataset_sample_size.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,410 +453,340 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>96</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>112</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>340</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>159</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>101</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>264</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>502</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>204</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>120</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>131</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>United States of America</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
         <v>81</v>
       </c>
     </row>
